--- a/artfynd/A 51010-2025 artfynd.xlsx
+++ b/artfynd/A 51010-2025 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>128532975</v>
       </c>
       <c r="B8" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>128532976</v>
       </c>
       <c r="B9" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>128532977</v>
       </c>
       <c r="B10" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
